--- a/daily_matches/job_matches_2026-08-10.xlsx
+++ b/daily_matches/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Applied Artificial Intelligence Scientist III</t>
+          <t>Personalization Product Senior Data Associate</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Azure ML, Git, Snowflake, Databricks, PySpark</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853f4fc1b6c4d0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee342097369dcac</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Science Team- Boise, ID</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Prompt Engineering, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9cae4f9c3b33d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=15d09dc910699334</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,147 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efb7ac07ab648ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9ee80d0da4c4aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Software Engineer, Product Experience</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Verse</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, Docker, Kubernetes, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c8098355371d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=054aa1dc99200216</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CCS Inc</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, PyTorch, AWS SageMaker, Azure ML, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b827883dd79b3647</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed94d4000dbeac4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-10.xlsx
+++ b/daily_matches/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,105 +468,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Personalization Product Senior Data Associate</t>
+          <t>Software Development Engineer - Adobe Firefly Web</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee342097369dcac</t>
+          <t>https://www.indeed.com/viewjob?jk=13ba4e5643574844</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Aderant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d09dc910699334</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed94d4000dbeac4</t>
+          <t>https://www.indeed.com/viewjob?jk=061b33385aba242d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-10.xlsx
+++ b/daily_matches/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Adobe Firefly Web</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Optimization</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,217 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ba4e5643574844</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aderant</t>
+          <t>Doble Engineering Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Marlborough, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, Git, Databricks, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ee2aec48a20d562</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior AI/Full-Stack Software Engineer(Part-Time)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MODULAR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ceda01afff0d734</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Java)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hiring Data Engineers in USA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V4C.ai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI Engineer 4A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=061b33385aba242d</t>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f17daa76004ab72</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Technical Product Owner/Business Analyst (Remote - US)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nextech Systems</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, Databricks, Tableau, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddba282382509b0d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-10.xlsx
+++ b/daily_matches/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Senior AI Engineer (Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=bbdc56aa8fd0f845</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer AI</t>
+          <t>Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Doble Engineering Company</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, Git, Databricks, PostgreSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Snowflake, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee2aec48a20d562</t>
+          <t>https://www.indeed.com/viewjob?jk=c18bea9cda0cf7f1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI/Full-Stack Software Engineer(Part-Time)</t>
+          <t>Senior Software Engineer/Full Stack Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MODULAR</t>
+          <t>PTMA Financial Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ceda01afff0d734</t>
+          <t>https://www.indeed.com/viewjob?jk=c682fc9ace07d7fa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Senior Software Engineer/Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PTMA Financial Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
+          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,112 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hiring Data Engineers in USA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>V4C.ai</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AI Engineer 4A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f17daa76004ab72</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Technical Product Owner/Business Analyst (Remote - US)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Nextech Systems</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Data Lake, Databricks, Tableau, Power BI, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddba282382509b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=b310f9fae385df3d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-10.xlsx
+++ b/daily_matches/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Remote)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbdc56aa8fd0f845</t>
+          <t>https://www.indeed.com/viewjob?jk=0d76a58347bab72d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Solution Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Snowflake, R, Scala, Optimization</t>
+          <t>RAG, S3, Redshift, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c18bea9cda0cf7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd470eb429ea88c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer/Full Stack Developer</t>
+          <t>Senior Software Engineer - Murex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PTMA Financial Solutions</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Glue, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,742 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682fc9ace07d7fa</t>
+          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer/Full Stack Developer</t>
+          <t>Senior Software Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PTMA Financial Solutions</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Databricks, PySpark, PostgreSQL, MongoDB, Cassandra, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Teleflex</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bd3c383bbc14178</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Remote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, PySpark, Hadoop, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57ea84787b8db583</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf9556b1329661f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d9231715639f7b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28576e82cfb86839</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5ea1834eefc01ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9d18f7c33b8eeff</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd41b34a09d8eb42</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Agentic Science/Generative Models, AI for Biology &amp; Translation (AIBT)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a49287f0fa45715</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Agentic Science/Generative Models, AI for Biology &amp; Translation (AIBT)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0296a10142edd65a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Artic Consulting, Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Dataflow, Git, Snowflake, PySpark, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Hybrid in Schaumburg, IL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, FastAPI, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=781fb6a950bdd1bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Cloud Engineering (Contractor)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Aliso Viejo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b7ea069889ed966</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior AI DevOps Developer [584]</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D-Wave</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b777e9922474a9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Consultant</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UNICON SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=667a8e4c882aa4ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a499aa89f203fdc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc27aa368dddc6fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Quality Assurance Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Citian</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3959614a0ae434be</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>National Interstate</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Richfield, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b310f9fae385df3d</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cc61d973b5745a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>National Interstate</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c26cbec3a0994f4f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-10.xlsx
+++ b/daily_matches/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>VIANT TECHNOLOGY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery, MySQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d76a58347bab72d</t>
+          <t>https://www.indeed.com/viewjob?jk=5affcc09d0cdd66c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Redshift, Kafka</t>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, PySpark, Hadoop, MongoDB, Cassandra, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd470eb429ea88c</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Murex</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Glue, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, Kafka, Python</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Radiant Infotech</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, PySpark, PostgreSQL, MongoDB, Cassandra, NoSQL, Power BI</t>
+          <t>LangChain, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1be19c6580ca37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Software Development Engineer III - GenAI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Teleflex</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd3c383bbc14178</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5736834d2b4baa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Remote</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, PySpark, Hadoop, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ea84787b8db583</t>
+          <t>https://www.indeed.com/viewjob?jk=c7013d94a0d0c9a6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,207 +706,207 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf9556b1329661f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad184ef3ec78ca2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9231715639f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c54e469d1e10e196</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28576e82cfb86839</t>
+          <t>https://www.indeed.com/viewjob?jk=e31707a26ca94955</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ea1834eefc01ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e31020c3e212577e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d18f7c33b8eeff</t>
+          <t>https://www.indeed.com/viewjob?jk=d15ea72cf878788d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer, PEG AI and Machine Learning Engineering</t>
+          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Git, Databricks</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd41b34a09d8eb42</t>
+          <t>https://www.indeed.com/viewjob?jk=586a6ef23c2b2162</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Agentic Science/Generative Models, AI for Biology &amp; Translation (AIBT)</t>
+          <t>Machine Learning Engineer Intern - Computer Vision Focused</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Accurate Systems Engineering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a49287f0fa45715</t>
+          <t>https://www.indeed.com/viewjob?jk=39159e71ab608cf3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Agentic Science/Generative Models, AI for Biology &amp; Translation (AIBT)</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Alpha Nodus, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>S3, AKS, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0296a10142edd65a</t>
+          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>AI Infra Advisory Researcher</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, Git, Snowflake, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Data Lake, Kubernetes, Kafka, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=6739b3d7e072f7b2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid in Schaumburg, IL</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, FastAPI, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,287 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781fb6a950bdd1bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Cloud Engineering (Contractor)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PlayStation</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Aliso Viejo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ea069889ed966</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior AI DevOps Developer [584]</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D-Wave</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b777e9922474a9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AI Consultant</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>UNICON SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=667a8e4c882aa4ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Iselin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a499aa89f203fdc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc27aa368dddc6fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Citian</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3959614a0ae434be</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Software Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>National Interstate</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Richfield, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, SQL, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc61d973b5745a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Software Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>National Interstate</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, SQL, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c26cbec3a0994f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-10.xlsx
+++ b/daily_matches/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VIANT TECHNOLOGY</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery, MySQL, Python</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5affcc09d0cdd66c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a32054447bc409c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Snowflake, PySpark, Hadoop, MongoDB, Cassandra, Python</t>
+          <t>AI Engineer, Data Scientist, Azure ML, BigQuery, AKS, CI/CD, GitHub Actions, Git, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>eBusiness Solutions Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=32ce2d1b44956999</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Radiant Infotech</t>
+          <t>siriiKon Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1be19c6580ca37</t>
+          <t>https://www.indeed.com/viewjob?jk=04d85c743609a480</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Development Engineer III - GenAI</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Git, Python, R, Java</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5736834d2b4baa</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python, SQL</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7013d94a0d0c9a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad184ef3ec78ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
+          <t>AI Engineer – Center of Excellence</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aderant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54e469d1e10e196</t>
+          <t>https://www.indeed.com/viewjob?jk=83e97649b602e2a6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
+          <t>Senior AI Developer (Full‑Stack) (contract)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31707a26ca94955</t>
+          <t>https://www.indeed.com/viewjob?jk=81505650873830b1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+          <t>RAG, Data Lake, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31020c3e212577e</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
+          <t>Full Stack Engineer (AI, Automation &amp; CRM Integrations) - USA Residents Only</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Automation Agency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+          <t>LangChain, RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,182 +846,882 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15ea72cf878788d</t>
+          <t>https://www.indeed.com/viewjob?jk=047e4a6bf28263c9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Angular / Node.js / TypeScript)</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586a6ef23c2b2162</t>
+          <t>https://www.indeed.com/viewjob?jk=59553610544ec099</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern - Computer Vision Focused</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Accurate Systems Engineering</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Git, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39159e71ab608cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=50efc89a6f5f01d3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alpha Nodus, Inc.</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, AKS, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f628e303f32fb3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Infra Advisory Researcher</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Data Lake, Kubernetes, Kafka, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739b3d7e072f7b2</t>
+          <t>https://www.indeed.com/viewjob?jk=f73e65c504af56a9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, Terraform, Databricks</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=178640839de1004f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>(USA) Senior, Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8a9ec7bdd3d2ed3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer in Test - Datacenter Server OS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9be6a830e5f5df3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Cloud Engineering (Contractor)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Aliso Viejo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3652d2db14f557e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer I – AI Agents &amp; Harnesses</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1bda0a5bf47e711</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fab3c569582f4c21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Cloud Operations Engineer, Deployments</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pegasystems</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Docker, Kubernetes, PostgreSQL, MongoDB, Cassandra, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8544f2004dc0b3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Weyerhaeuser</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Snowflake, Power BI, Matplotlib, Python, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f90266ab1f3211f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior AI-ML Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a2ccaf834778698</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer, Core AI Software</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Keras, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a76022357e22783b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Strategic Education, Inc.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=438fe63917570ca4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer, Developer Productivity</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>The Mind Company</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5216fabfc34f0478</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62f693afdc2b2e46</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI Product Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bungalow</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, FastAPI, Terraform, Redshift, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2fd5008577dd063</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Penlink</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e988123fd077c7ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Developer - AI Platform</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Geotab</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Docker, Kubernetes, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1605559a1c1f8cd3</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-10.xlsx
+++ b/daily_matches/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI/ML Solutions Architect - MySQL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow, PyTorch, XGBoost</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a32054447bc409c</t>
+          <t>https://www.indeed.com/viewjob?jk=a67ae1ade25d4115</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>26.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Azure ML, BigQuery, AKS, CI/CD, GitHub Actions, Git, Databricks, BigQuery</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eBusiness Solutions Inc.</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ce2d1b44956999</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>siriiKon Inc.</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python</t>
+          <t>RAG, OpenCV, S3, EC2, Docker, CI/CD, Git, Databricks, PySpark, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d85c743609a480</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Scientist, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=62b7232e7951bd03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Senior Scientist Data Science</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>MonoSol LLC.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, LightGBM, Git, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a237dccbbc5db828</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer – Center of Excellence</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aderant</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e97649b602e2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Developer (Full‑Stack) (contract)</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Snowflake, Databricks, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81505650873830b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, PySpark, Hadoop, MongoDB, Cassandra, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (AI, Automation &amp; CRM Integrations) - USA Residents Only</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Automation Agency</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047e4a6bf28263c9</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
@@ -876,29 +876,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59553610544ec099</t>
+          <t>https://www.indeed.com/viewjob?jk=d86089c20137f9e6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, Terraform, Databricks</t>
+          <t>RAG, S3, FastAPI, Docker, CI/CD, Git, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50efc89a6f5f01d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3a1029cc698e24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,112 +941,112 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, Terraform, Databricks</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f628e303f32fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, Terraform, Databricks</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73e65c504af56a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f78c5133207a9c11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Data Scientist &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Chobani</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, Terraform, Databricks</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178640839de1004f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0a97c49076b248</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bureau Veritas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Copilot, FastAPI, Docker, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f844e46482fa7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(USA) Senior, Software Engineer</t>
+          <t>Software Engineer I - AI Agents</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Observe.AI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a9ec7bdd3d2ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba451abb3013508</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test - Datacenter Server OS</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R</t>
+          <t>CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9be6a830e5f5df3</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Cloud Engineering (Contractor)</t>
+          <t>Associate - Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Mitsui Sumitomo Insurance Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Data Lake, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3652d2db14f557e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d294fea3f38a719d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Site Reliability Engineer, AI Infrastructure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+          <t>https://www.indeed.com/viewjob?jk=00357e4d9ab44574</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SlickDevs.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, LangChain, CI/CD, Snowflake, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5efced4511993d6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Agents &amp; Harnesses</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Aquila Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1bda0a5bf47e711</t>
+          <t>https://www.indeed.com/viewjob?jk=ea147adb7722a869</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab3c569582f4c21</t>
+          <t>https://www.indeed.com/viewjob?jk=428e91fd0a267cfe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer, Deployments</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, Kubernetes, PostgreSQL, MongoDB, Cassandra, SQL, R, Java</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8544f2004dc0b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=af87e70a3f78ee17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Associate Data Scientist, Tools &amp; Automation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,357 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Weyerhaeuser</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Snowflake, Power BI, Matplotlib, Python, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f90266ab1f3211f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior AI-ML Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mayo Clinic</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a2ccaf834778698</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Software Engineer, Core AI Software</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Keras, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a76022357e22783b</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Strategic Education, Inc.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=438fe63917570ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer, Developer Productivity</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>The Mind Company</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, AKS, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5216fabfc34f0478</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62f693afdc2b2e46</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>AI Product Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Bungalow</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, FastAPI, Terraform, Redshift, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fd5008577dd063</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Penlink</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e988123fd077c7ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Developer - AI Platform</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Geotab</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, Docker, Kubernetes, BigQuery, Python, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1605559a1c1f8cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb80c5fb1a52189</t>
         </is>
       </c>
     </row>
